--- a/argus/kship/models/085310_model.xlsx
+++ b/argus/kship/models/085310_model.xlsx
@@ -672,37 +672,37 @@
     <comment ref="AH21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 154514억 × 비례계수 0.0115 × 계절비중 Q3 0.208(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.96, n=12, 창 12)</t>
+고객지수 4분기 이동합(t−4) 154515억 × 비례계수 0.0115 × 계절비중 Q3 0.208(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.96, n=12, 창 12)</t>
       </text>
     </comment>
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 162244억 × 비례계수 0.0115 × 계절비중 Q4 0.317(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.96, n=12, 창 12)</t>
+고객지수 4분기 이동합(t−4) 162316억 × 비례계수 0.0115 × 계절비중 Q4 0.317(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.96, n=12, 창 12)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 168148억 × 비례계수 0.0115 × 계절비중 Q1 0.234(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.96, n=12, 창 12)</t>
+고객지수 4분기 이동합(t−4) 168288억 × 비례계수 0.0115 × 계절비중 Q1 0.234(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.96, n=12, 창 12)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 166248억 × 비례계수 0.0115 × 계절비중 Q2 0.241(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.96, n=12, 창 12)</t>
+고객지수 4분기 이동합(t−4) 166732억 × 비례계수 0.0115 × 계절비중 Q2 0.241(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.96, n=12, 창 12)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 165576억 × 비례계수 0.0115 × 계절비중 Q3 0.208(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.96, n=12, 창 12)</t>
+고객지수 4분기 이동합(t−4) 166122억 × 비례계수 0.0115 × 계절비중 Q3 0.208(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.96, n=12, 창 12)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 164079억 × 비례계수 0.0115 × 계절비중 Q4 0.317(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.96, n=12, 창 12)</t>
+고객지수 4분기 이동합(t−4) 164619억 × 비례계수 0.0115 × 계절비중 Q4 0.317(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.96, n=12, 창 12)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -1731,37 +1731,37 @@
     </comment>
     <comment ref="AH5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 154514억 × 비례계수 0.0115 × 계절비중 Q3 0.208(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.96, n=12, 창 12)
+        <t>추정: 고객지수 4분기 이동합(t−4) 154515억 × 비례계수 0.0115 × 계절비중 Q3 0.208(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.96, n=12, 창 12)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 162244억 × 비례계수 0.0115 × 계절비중 Q4 0.317(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.96, n=12, 창 12)
+        <t>추정: 고객지수 4분기 이동합(t−4) 162316억 × 비례계수 0.0115 × 계절비중 Q4 0.317(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.96, n=12, 창 12)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 168148억 × 비례계수 0.0115 × 계절비중 Q1 0.234(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.96, n=12, 창 12)
+        <t>추정: 고객지수 4분기 이동합(t−4) 168288억 × 비례계수 0.0115 × 계절비중 Q1 0.234(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.96, n=12, 창 12)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 166248억 × 비례계수 0.0115 × 계절비중 Q2 0.241(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.96, n=12, 창 12)
+        <t>추정: 고객지수 4분기 이동합(t−4) 166732억 × 비례계수 0.0115 × 계절비중 Q2 0.241(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.96, n=12, 창 12)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 165576억 × 비례계수 0.0115 × 계절비중 Q3 0.208(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.96, n=12, 창 12)
+        <t>추정: 고객지수 4분기 이동합(t−4) 166122억 × 비례계수 0.0115 × 계절비중 Q3 0.208(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.96, n=12, 창 12)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 164079억 × 비례계수 0.0115 × 계절비중 Q4 0.317(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.96, n=12, 창 12)
+        <t>추정: 고객지수 4분기 이동합(t−4) 164619억 × 비례계수 0.0115 × 계절비중 Q4 0.317(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.96, n=12, 창 12)
 [yoy]</t>
       </text>
     </comment>
@@ -6426,20 +6426,20 @@
         <v>0.182633</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.227639</v>
+        <v>0.228199</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>0.228577</v>
+        <v>0.229609</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>0.135277</v>
+        <v>0.138579</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>0.071587</v>
+        <v>0.075131</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>0.011321</v>
+        <v>0.014187</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -6575,23 +6575,23 @@
         <v>0.161923</v>
       </c>
       <c r="AI22" s="24" t="n">
-        <v>0.161924</v>
+        <v>0.161918</v>
       </c>
       <c r="AJ22" s="25">
         <f>IFERROR(subQ!AJ8/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK22" s="24" t="n">
-        <v>0.161923</v>
+        <v>0.16192</v>
       </c>
       <c r="AL22" s="24" t="n">
-        <v>0.161923</v>
+        <v>0.16193</v>
       </c>
       <c r="AM22" s="24" t="n">
-        <v>0.161937</v>
+        <v>0.161932</v>
       </c>
       <c r="AN22" s="24" t="n">
-        <v>0.161933</v>
+        <v>0.161918</v>
       </c>
       <c r="AO22" s="25">
         <f>IFERROR(subQ!AO8/subQ!AO5,"")</f>
@@ -6730,23 +6730,23 @@
         <v>-0.014069</v>
       </c>
       <c r="AI23" s="24" t="n">
-        <v>-0.014058</v>
+        <v>-0.014069</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>-0.014065</v>
+        <v>-0.014053</v>
       </c>
       <c r="AL23" s="24" t="n">
+        <v>-0.01407</v>
+      </c>
+      <c r="AM23" s="24" t="n">
         <v>-0.014067</v>
       </c>
-      <c r="AM23" s="24" t="n">
-        <v>-0.014063</v>
-      </c>
       <c r="AN23" s="24" t="n">
-        <v>-0.014068</v>
+        <v>-0.014055</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -7482,7 +7482,7 @@
         <v>-0</v>
       </c>
       <c r="AM28" s="24" t="n">
-        <v>0.066667</v>
+        <v>0.035714</v>
       </c>
       <c r="AN28" s="24" t="n">
         <v>-0</v>
@@ -8117,16 +8117,16 @@
       </c>
       <c r="AJ33" s="30" t="n"/>
       <c r="AK33" s="29" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="AL33" s="29" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.7</v>
       </c>
       <c r="AM33" s="29" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="AN33" s="29" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="AO33" s="30" t="n"/>
     </row>
@@ -8461,16 +8461,16 @@
       </c>
       <c r="AJ36" s="25" t="n"/>
       <c r="AK36" s="24" t="n">
-        <v>-0.000608</v>
+        <v>-0.000621</v>
       </c>
       <c r="AL36" s="24" t="n">
-        <v>-0.001669</v>
+        <v>-0.001695</v>
       </c>
       <c r="AM36" s="24" t="n">
-        <v>0.000363</v>
+        <v>0.00035</v>
       </c>
       <c r="AN36" s="24" t="n">
-        <v>-0.003291</v>
+        <v>-0.003343</v>
       </c>
       <c r="AO36" s="25" t="n"/>
     </row>
@@ -9522,23 +9522,23 @@
         <v>-0.014069</v>
       </c>
       <c r="AI45" s="24" t="n">
-        <v>-0.014058</v>
+        <v>-0.014069</v>
       </c>
       <c r="AJ45" s="25">
         <f>IFERROR(subQ!AJ36/subQ!AJ35,"")</f>
         <v/>
       </c>
       <c r="AK45" s="24" t="n">
-        <v>-0.014065</v>
+        <v>-0.014053</v>
       </c>
       <c r="AL45" s="24" t="n">
+        <v>-0.01407</v>
+      </c>
+      <c r="AM45" s="24" t="n">
         <v>-0.014067</v>
       </c>
-      <c r="AM45" s="24" t="n">
-        <v>-0.014063</v>
-      </c>
       <c r="AN45" s="24" t="n">
-        <v>-0.014068</v>
+        <v>-0.014055</v>
       </c>
       <c r="AO45" s="25">
         <f>IFERROR(subQ!AO36/subQ!AO35,"")</f>

--- a/argus/kship/models/085310_model.xlsx
+++ b/argus/kship/models/085310_model.xlsx
@@ -648,61 +648,61 @@
     <comment ref="AC21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 130653억 × 비례계수 0.0115 × 계절비중 Q3 0.208(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.96, n=12, 창 12)</t>
+전년동기 × (1+30.2%) — g=최근 4분기 합 YoY 30.2% 클립(−30~+50%), 연차별 절반 감쇠(가정)</t>
       </text>
     </comment>
     <comment ref="AD21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 132158억 × 비례계수 0.0115 × 계절비중 Q4 0.317(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.96, n=12, 창 12)</t>
+전년동기 × (1+30.2%) — g=최근 4분기 합 YoY 30.2% 클립(−30~+50%), 연차별 절반 감쇠(가정)</t>
       </text>
     </comment>
     <comment ref="AF21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 136866억 × 비례계수 0.0115 × 계절비중 Q1 0.234(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.96, n=12, 창 12)</t>
+전년동기 × (1+30.2%) — g=최근 4분기 합 YoY 30.2% 클립(−30~+50%), 연차별 절반 감쇠(가정)</t>
       </text>
     </comment>
     <comment ref="AG21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 146437억 × 비례계수 0.0115 × 계절비중 Q2 0.241(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.96, n=12, 창 12)</t>
+전년동기 × (1+30.2%) — g=최근 4분기 합 YoY 30.2% 클립(−30~+50%), 연차별 절반 감쇠(가정)</t>
       </text>
     </comment>
     <comment ref="AH21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 154515억 × 비례계수 0.0115 × 계절비중 Q3 0.208(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.96, n=12, 창 12)</t>
+전년동기 × (1+15.1%) — g=최근 4분기 합 YoY 30.2% 클립(−30~+50%), 연차별 절반 감쇠(가정)</t>
       </text>
     </comment>
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 162316억 × 비례계수 0.0115 × 계절비중 Q4 0.317(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.96, n=12, 창 12)</t>
+전년동기 × (1+15.1%) — g=최근 4분기 합 YoY 30.2% 클립(−30~+50%), 연차별 절반 감쇠(가정)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 168288억 × 비례계수 0.0115 × 계절비중 Q1 0.234(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.96, n=12, 창 12)</t>
+전년동기 × (1+15.1%) — g=최근 4분기 합 YoY 30.2% 클립(−30~+50%), 연차별 절반 감쇠(가정)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 166732억 × 비례계수 0.0115 × 계절비중 Q2 0.241(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.96, n=12, 창 12)</t>
+전년동기 × (1+15.1%) — g=최근 4분기 합 YoY 30.2% 클립(−30~+50%), 연차별 절반 감쇠(가정)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 166122억 × 비례계수 0.0115 × 계절비중 Q3 0.208(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.96, n=12, 창 12)</t>
+전년동기 × (1+7.6%) — g=최근 4분기 합 YoY 30.2% 클립(−30~+50%), 연차별 절반 감쇠(가정)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 164619억 × 비례계수 0.0115 × 계절비중 Q4 0.317(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.96, n=12, 창 12)</t>
+전년동기 × (1+7.6%) — g=최근 4분기 합 YoY 30.2% 클립(−30~+50%), 연차별 절반 감쇠(가정)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -768,121 +768,121 @@
     <comment ref="AC23" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출액
-매출액 × OPM(최근 8분기 OPM 중위 -1.4% 유지)</t>
+매출액 × OPM(최근 8분기 OPM 중위 -1.4% 유지(클립 −20~40%))</t>
       </text>
     </comment>
     <comment ref="AD23" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출액
-매출액 × OPM(최근 8분기 OPM 중위 -1.4% 유지)</t>
+매출액 × OPM(최근 8분기 OPM 중위 -1.4% 유지(클립 −20~40%))</t>
       </text>
     </comment>
     <comment ref="AF23" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출액
-매출액 × OPM(최근 8분기 OPM 중위 -1.4% 유지)</t>
+매출액 × OPM(최근 8분기 OPM 중위 -1.4% 유지(클립 −20~40%))</t>
       </text>
     </comment>
     <comment ref="AG23" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출액
-매출액 × OPM(최근 8분기 OPM 중위 -1.4% 유지)</t>
+매출액 × OPM(최근 8분기 OPM 중위 -1.4% 유지(클립 −20~40%))</t>
       </text>
     </comment>
     <comment ref="AH23" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출액
-매출액 × OPM(최근 8분기 OPM 중위 -1.4% 유지)</t>
+매출액 × OPM(최근 8분기 OPM 중위 -1.4% 유지(클립 −20~40%))</t>
       </text>
     </comment>
     <comment ref="AI23" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출액
-매출액 × OPM(최근 8분기 OPM 중위 -1.4% 유지)</t>
+매출액 × OPM(최근 8분기 OPM 중위 -1.4% 유지(클립 −20~40%))</t>
       </text>
     </comment>
     <comment ref="AK23" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출액
-매출액 × OPM(최근 8분기 OPM 중위 -1.4% 유지)</t>
+매출액 × OPM(최근 8분기 OPM 중위 -1.4% 유지(클립 −20~40%))</t>
       </text>
     </comment>
     <comment ref="AL23" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출액
-매출액 × OPM(최근 8분기 OPM 중위 -1.4% 유지)</t>
+매출액 × OPM(최근 8분기 OPM 중위 -1.4% 유지(클립 −20~40%))</t>
       </text>
     </comment>
     <comment ref="AM23" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출액
-매출액 × OPM(최근 8분기 OPM 중위 -1.4% 유지)</t>
+매출액 × OPM(최근 8분기 OPM 중위 -1.4% 유지(클립 −20~40%))</t>
       </text>
     </comment>
     <comment ref="AN23" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출액
-매출액 × OPM(최근 8분기 OPM 중위 -1.4% 유지)</t>
+매출액 × OPM(최근 8분기 OPM 중위 -1.4% 유지(클립 −20~40%))</t>
       </text>
     </comment>
     <comment ref="AC24" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-최근 8분기 OPM 중위 -1.4% 유지</t>
+최근 8분기 OPM 중위 -1.4% 유지(클립 −20~40%)</t>
       </text>
     </comment>
     <comment ref="AD24" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-최근 8분기 OPM 중위 -1.4% 유지</t>
+최근 8분기 OPM 중위 -1.4% 유지(클립 −20~40%)</t>
       </text>
     </comment>
     <comment ref="AF24" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-최근 8분기 OPM 중위 -1.4% 유지</t>
+최근 8분기 OPM 중위 -1.4% 유지(클립 −20~40%)</t>
       </text>
     </comment>
     <comment ref="AG24" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-최근 8분기 OPM 중위 -1.4% 유지</t>
+최근 8분기 OPM 중위 -1.4% 유지(클립 −20~40%)</t>
       </text>
     </comment>
     <comment ref="AH24" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-최근 8분기 OPM 중위 -1.4% 유지</t>
+최근 8분기 OPM 중위 -1.4% 유지(클립 −20~40%)</t>
       </text>
     </comment>
     <comment ref="AI24" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-최근 8분기 OPM 중위 -1.4% 유지</t>
+최근 8분기 OPM 중위 -1.4% 유지(클립 −20~40%)</t>
       </text>
     </comment>
     <comment ref="AK24" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-최근 8분기 OPM 중위 -1.4% 유지</t>
+최근 8분기 OPM 중위 -1.4% 유지(클립 −20~40%)</t>
       </text>
     </comment>
     <comment ref="AL24" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-최근 8분기 OPM 중위 -1.4% 유지</t>
+최근 8분기 OPM 중위 -1.4% 유지(클립 −20~40%)</t>
       </text>
     </comment>
     <comment ref="AM24" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-최근 8분기 OPM 중위 -1.4% 유지</t>
+최근 8분기 OPM 중위 -1.4% 유지(클립 −20~40%)</t>
       </text>
     </comment>
     <comment ref="AN24" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-최근 8분기 OPM 중위 -1.4% 유지</t>
+최근 8분기 OPM 중위 -1.4% 유지(클립 −20~40%)</t>
       </text>
     </comment>
     <comment ref="AC25" authorId="0" shapeId="0">
@@ -894,57 +894,57 @@
     <comment ref="AD25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 776억 × 3.04% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 775억 × 3.04% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AF25" authorId="0" shapeId="0">
-      <text>
-        <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 775억 × 3.04% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
-      </text>
-    </comment>
-    <comment ref="AG25" authorId="0" shapeId="0">
-      <text>
-        <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 776억 × 3.04% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
-      </text>
-    </comment>
-    <comment ref="AH25" authorId="0" shapeId="0">
-      <text>
-        <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 775억 × 3.04% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
-      </text>
-    </comment>
-    <comment ref="AI25" authorId="0" shapeId="0">
-      <text>
-        <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 776억 × 3.04% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
-      </text>
-    </comment>
-    <comment ref="AK25" authorId="0" shapeId="0">
-      <text>
-        <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 773억 × 3.04% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
-      </text>
-    </comment>
-    <comment ref="AL25" authorId="0" shapeId="0">
-      <text>
-        <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 773억 × 3.04% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
-      </text>
-    </comment>
-    <comment ref="AM25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
 이자손익 = 이자발생자산 772억 × 3.04% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
-    <comment ref="AN25" authorId="0" shapeId="0">
+    <comment ref="AG25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
 이자손익 = 이자발생자산 772억 × 3.04% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
+    <comment ref="AH25" authorId="0" shapeId="0">
+      <text>
+        <t>모델값 역산(implied): 모델 v 그대로
+이자손익 = 이자발생자산 770억 × 3.04% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+      </text>
+    </comment>
+    <comment ref="AI25" authorId="0" shapeId="0">
+      <text>
+        <t>모델값 역산(implied): 모델 v 그대로
+이자손익 = 이자발생자산 770억 × 3.04% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+      </text>
+    </comment>
+    <comment ref="AK25" authorId="0" shapeId="0">
+      <text>
+        <t>모델값 역산(implied): 모델 v 그대로
+이자손익 = 이자발생자산 766억 × 3.04% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+      </text>
+    </comment>
+    <comment ref="AL25" authorId="0" shapeId="0">
+      <text>
+        <t>모델값 역산(implied): 모델 v 그대로
+이자손익 = 이자발생자산 765억 × 3.04% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+      </text>
+    </comment>
+    <comment ref="AM25" authorId="0" shapeId="0">
+      <text>
+        <t>모델값 역산(implied): 모델 v 그대로
+이자손익 = 이자발생자산 762억 × 3.04% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+      </text>
+    </comment>
+    <comment ref="AN25" authorId="0" shapeId="0">
+      <text>
+        <t>모델값 역산(implied): 모델 v 그대로
+이자손익 = 이자발생자산 762억 × 3.04% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+      </text>
+    </comment>
     <comment ref="AC26" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
@@ -1501,18 +1501,6 @@
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
 직전 결산 DPS 10원 유지</t>
-      </text>
-    </comment>
-    <comment ref="AG42" authorId="0" shapeId="0">
-      <text>
-        <t>모델값 역산(implied): v / 전년동기 − 1
-현재 종가 ÷ TTM EPS(추정 포함)</t>
-      </text>
-    </comment>
-    <comment ref="AH42" authorId="0" shapeId="0">
-      <text>
-        <t>모델값 역산(implied): v / 전년동기 − 1
-현재 종가 ÷ TTM EPS(추정 포함)</t>
       </text>
     </comment>
     <comment ref="AC43" authorId="0" shapeId="0">
@@ -1707,61 +1695,61 @@
   <commentList>
     <comment ref="AC5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 130653억 × 비례계수 0.0115 × 계절비중 Q3 0.208(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.96, n=12, 창 12)
+        <t>추정: 전년동기 × (1+30.2%) — g=최근 4분기 합 YoY 30.2% 클립(−30~+50%), 연차별 절반 감쇠(가정)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AD5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 132158억 × 비례계수 0.0115 × 계절비중 Q4 0.317(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.96, n=12, 창 12)
+        <t>추정: 전년동기 × (1+30.2%) — g=최근 4분기 합 YoY 30.2% 클립(−30~+50%), 연차별 절반 감쇠(가정)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AF5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 136866억 × 비례계수 0.0115 × 계절비중 Q1 0.234(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.96, n=12, 창 12)
+        <t>추정: 전년동기 × (1+30.2%) — g=최근 4분기 합 YoY 30.2% 클립(−30~+50%), 연차별 절반 감쇠(가정)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AG5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 146437억 × 비례계수 0.0115 × 계절비중 Q2 0.241(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.96, n=12, 창 12)
+        <t>추정: 전년동기 × (1+30.2%) — g=최근 4분기 합 YoY 30.2% 클립(−30~+50%), 연차별 절반 감쇠(가정)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AH5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 154515억 × 비례계수 0.0115 × 계절비중 Q3 0.208(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.96, n=12, 창 12)
+        <t>추정: 전년동기 × (1+15.1%) — g=최근 4분기 합 YoY 30.2% 클립(−30~+50%), 연차별 절반 감쇠(가정)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 162316억 × 비례계수 0.0115 × 계절비중 Q4 0.317(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.96, n=12, 창 12)
+        <t>추정: 전년동기 × (1+15.1%) — g=최근 4분기 합 YoY 30.2% 클립(−30~+50%), 연차별 절반 감쇠(가정)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 168288억 × 비례계수 0.0115 × 계절비중 Q1 0.234(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.96, n=12, 창 12)
+        <t>추정: 전년동기 × (1+15.1%) — g=최근 4분기 합 YoY 30.2% 클립(−30~+50%), 연차별 절반 감쇠(가정)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 166732억 × 비례계수 0.0115 × 계절비중 Q2 0.241(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.96, n=12, 창 12)
+        <t>추정: 전년동기 × (1+15.1%) — g=최근 4분기 합 YoY 30.2% 클립(−30~+50%), 연차별 절반 감쇠(가정)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 166122억 × 비례계수 0.0115 × 계절비중 Q3 0.208(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.96, n=12, 창 12)
+        <t>추정: 전년동기 × (1+7.6%) — g=최근 4분기 합 YoY 30.2% 클립(−30~+50%), 연차별 절반 감쇠(가정)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 164619억 × 비례계수 0.0115 × 계절비중 Q4 0.317(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.96, n=12, 창 12)
+        <t>추정: 전년동기 × (1+7.6%) — g=최근 4분기 합 YoY 30.2% 클립(−30~+50%), 연차별 절반 감쇠(가정)
 [yoy]</t>
       </text>
     </comment>
@@ -1947,61 +1935,61 @@
     </comment>
     <comment ref="AC9" authorId="0" shapeId="0">
       <text>
-        <t>추정: 매출액 × OPM(최근 8분기 OPM 중위 -1.4% 유지)
+        <t>추정: 매출액 × OPM(최근 8분기 OPM 중위 -1.4% 유지(클립 −20~40%))
 [ratio]</t>
       </text>
     </comment>
     <comment ref="AD9" authorId="0" shapeId="0">
       <text>
-        <t>추정: 매출액 × OPM(최근 8분기 OPM 중위 -1.4% 유지)
+        <t>추정: 매출액 × OPM(최근 8분기 OPM 중위 -1.4% 유지(클립 −20~40%))
 [ratio]</t>
       </text>
     </comment>
     <comment ref="AF9" authorId="0" shapeId="0">
       <text>
-        <t>추정: 매출액 × OPM(최근 8분기 OPM 중위 -1.4% 유지)
+        <t>추정: 매출액 × OPM(최근 8분기 OPM 중위 -1.4% 유지(클립 −20~40%))
 [ratio]</t>
       </text>
     </comment>
     <comment ref="AG9" authorId="0" shapeId="0">
       <text>
-        <t>추정: 매출액 × OPM(최근 8분기 OPM 중위 -1.4% 유지)
+        <t>추정: 매출액 × OPM(최근 8분기 OPM 중위 -1.4% 유지(클립 −20~40%))
 [ratio]</t>
       </text>
     </comment>
     <comment ref="AH9" authorId="0" shapeId="0">
       <text>
-        <t>추정: 매출액 × OPM(최근 8분기 OPM 중위 -1.4% 유지)
+        <t>추정: 매출액 × OPM(최근 8분기 OPM 중위 -1.4% 유지(클립 −20~40%))
 [ratio]</t>
       </text>
     </comment>
     <comment ref="AI9" authorId="0" shapeId="0">
       <text>
-        <t>추정: 매출액 × OPM(최근 8분기 OPM 중위 -1.4% 유지)
+        <t>추정: 매출액 × OPM(최근 8분기 OPM 중위 -1.4% 유지(클립 −20~40%))
 [ratio]</t>
       </text>
     </comment>
     <comment ref="AK9" authorId="0" shapeId="0">
       <text>
-        <t>추정: 매출액 × OPM(최근 8분기 OPM 중위 -1.4% 유지)
+        <t>추정: 매출액 × OPM(최근 8분기 OPM 중위 -1.4% 유지(클립 −20~40%))
 [ratio]</t>
       </text>
     </comment>
     <comment ref="AL9" authorId="0" shapeId="0">
       <text>
-        <t>추정: 매출액 × OPM(최근 8분기 OPM 중위 -1.4% 유지)
+        <t>추정: 매출액 × OPM(최근 8분기 OPM 중위 -1.4% 유지(클립 −20~40%))
 [ratio]</t>
       </text>
     </comment>
     <comment ref="AM9" authorId="0" shapeId="0">
       <text>
-        <t>추정: 매출액 × OPM(최근 8분기 OPM 중위 -1.4% 유지)
+        <t>추정: 매출액 × OPM(최근 8분기 OPM 중위 -1.4% 유지(클립 −20~40%))
 [ratio]</t>
       </text>
     </comment>
     <comment ref="AN9" authorId="0" shapeId="0">
       <text>
-        <t>추정: 매출액 × OPM(최근 8분기 OPM 중위 -1.4% 유지)
+        <t>추정: 매출액 × OPM(최근 8분기 OPM 중위 -1.4% 유지(클립 −20~40%))
 [ratio]</t>
       </text>
     </comment>
@@ -2102,61 +2090,61 @@
     </comment>
     <comment ref="AC10" authorId="0" shapeId="0">
       <text>
-        <t>추정: 최근 8분기 OPM 중위 -1.4% 유지
+        <t>추정: 최근 8분기 OPM 중위 -1.4% 유지(클립 −20~40%)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AD10" authorId="0" shapeId="0">
       <text>
-        <t>추정: 최근 8분기 OPM 중위 -1.4% 유지
+        <t>추정: 최근 8분기 OPM 중위 -1.4% 유지(클립 −20~40%)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AF10" authorId="0" shapeId="0">
       <text>
-        <t>추정: 최근 8분기 OPM 중위 -1.4% 유지
+        <t>추정: 최근 8분기 OPM 중위 -1.4% 유지(클립 −20~40%)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AG10" authorId="0" shapeId="0">
       <text>
-        <t>추정: 최근 8분기 OPM 중위 -1.4% 유지
+        <t>추정: 최근 8분기 OPM 중위 -1.4% 유지(클립 −20~40%)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AH10" authorId="0" shapeId="0">
       <text>
-        <t>추정: 최근 8분기 OPM 중위 -1.4% 유지
+        <t>추정: 최근 8분기 OPM 중위 -1.4% 유지(클립 −20~40%)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AI10" authorId="0" shapeId="0">
       <text>
-        <t>추정: 최근 8분기 OPM 중위 -1.4% 유지
+        <t>추정: 최근 8분기 OPM 중위 -1.4% 유지(클립 −20~40%)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK10" authorId="0" shapeId="0">
       <text>
-        <t>추정: 최근 8분기 OPM 중위 -1.4% 유지
+        <t>추정: 최근 8분기 OPM 중위 -1.4% 유지(클립 −20~40%)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL10" authorId="0" shapeId="0">
       <text>
-        <t>추정: 최근 8분기 OPM 중위 -1.4% 유지
+        <t>추정: 최근 8분기 OPM 중위 -1.4% 유지(클립 −20~40%)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM10" authorId="0" shapeId="0">
       <text>
-        <t>추정: 최근 8분기 OPM 중위 -1.4% 유지
+        <t>추정: 최근 8분기 OPM 중위 -1.4% 유지(클립 −20~40%)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN10" authorId="0" shapeId="0">
       <text>
-        <t>추정: 최근 8분기 OPM 중위 -1.4% 유지
+        <t>추정: 최근 8분기 OPM 중위 -1.4% 유지(클립 −20~40%)
 [yoy]</t>
       </text>
     </comment>
@@ -2168,58 +2156,58 @@
     </comment>
     <comment ref="AD11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 776억 × 3.04% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
-[abs]</t>
-      </text>
-    </comment>
-    <comment ref="AF11" authorId="0" shapeId="0">
-      <text>
         <t>추정: 이자손익 = 이자발생자산 775억 × 3.04% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
-    <comment ref="AG11" authorId="0" shapeId="0">
-      <text>
-        <t>추정: 이자손익 = 이자발생자산 776억 × 3.04% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
-[abs]</t>
-      </text>
-    </comment>
-    <comment ref="AH11" authorId="0" shapeId="0">
-      <text>
-        <t>추정: 이자손익 = 이자발생자산 775억 × 3.04% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
-[abs]</t>
-      </text>
-    </comment>
-    <comment ref="AI11" authorId="0" shapeId="0">
-      <text>
-        <t>추정: 이자손익 = 이자발생자산 776억 × 3.04% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
-[abs]</t>
-      </text>
-    </comment>
-    <comment ref="AK11" authorId="0" shapeId="0">
-      <text>
-        <t>추정: 이자손익 = 이자발생자산 773억 × 3.04% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
-[abs]</t>
-      </text>
-    </comment>
-    <comment ref="AL11" authorId="0" shapeId="0">
-      <text>
-        <t>추정: 이자손익 = 이자발생자산 773억 × 3.04% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
-[abs]</t>
-      </text>
-    </comment>
-    <comment ref="AM11" authorId="0" shapeId="0">
+    <comment ref="AF11" authorId="0" shapeId="0">
       <text>
         <t>추정: 이자손익 = 이자발생자산 772억 × 3.04% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
-    <comment ref="AN11" authorId="0" shapeId="0">
+    <comment ref="AG11" authorId="0" shapeId="0">
       <text>
         <t>추정: 이자손익 = 이자발생자산 772억 × 3.04% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
+    <comment ref="AH11" authorId="0" shapeId="0">
+      <text>
+        <t>추정: 이자손익 = 이자발생자산 770억 × 3.04% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+[abs]</t>
+      </text>
+    </comment>
+    <comment ref="AI11" authorId="0" shapeId="0">
+      <text>
+        <t>추정: 이자손익 = 이자발생자산 770억 × 3.04% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+[abs]</t>
+      </text>
+    </comment>
+    <comment ref="AK11" authorId="0" shapeId="0">
+      <text>
+        <t>추정: 이자손익 = 이자발생자산 766억 × 3.04% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+[abs]</t>
+      </text>
+    </comment>
+    <comment ref="AL11" authorId="0" shapeId="0">
+      <text>
+        <t>추정: 이자손익 = 이자발생자산 765억 × 3.04% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+[abs]</t>
+      </text>
+    </comment>
+    <comment ref="AM11" authorId="0" shapeId="0">
+      <text>
+        <t>추정: 이자손익 = 이자발생자산 762억 × 3.04% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+[abs]</t>
+      </text>
+    </comment>
+    <comment ref="AN11" authorId="0" shapeId="0">
+      <text>
+        <t>추정: 이자손익 = 이자발생자산 762억 × 3.04% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+[abs]</t>
+      </text>
+    </comment>
     <comment ref="AC12" authorId="0" shapeId="0">
       <text>
         <t>추정: 일회성 미가정 → 0
@@ -3441,18 +3429,6 @@
     <comment ref="AF33" authorId="0" shapeId="0">
       <text>
         <t>추정(가정 셀 참조 불가 — 기준값 없음, 모델값 직접): 현재 종가 ÷ TTM EPS(추정 포함)</t>
-      </text>
-    </comment>
-    <comment ref="AG33" authorId="0" shapeId="0">
-      <text>
-        <t>추정: 현재 종가 ÷ TTM EPS(추정 포함)
-[yoy]</t>
-      </text>
-    </comment>
-    <comment ref="AH33" authorId="0" shapeId="0">
-      <text>
-        <t>추정: 현재 종가 ÷ TTM EPS(추정 포함)
-[yoy]</t>
       </text>
     </comment>
     <comment ref="E34" authorId="0" shapeId="0">
@@ -4234,7 +4210,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-09-30</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-02</t>
         </is>
       </c>
     </row>
@@ -4355,14 +4331,14 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>한계: 모델 quality.warnings — 감가상각비가 face·CF 에 없음(주석 미파싱) → EBITDA·EV/EBITDA 미산출</t>
+          <t>한계: 모델 quality.warnings — 매출 드라이버 폴백(고객 연동 OOS 기각 — 동결 2025Q2 이후 4분기 매출 WAPE 연동 8.3% &gt; 추세 6.6% × 1.10 (suppliers_mentions·시차 4·4분기 이동합·창 12, r=0.96 유의)): 전년동기 × (1+g) 추세 / 감가상각비가 face·CF 에 없음(주석 미파싱) → EBITDA·EV/EBITDA 미산출</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>백테스트: {"freeze": "2025Q2", "horizon": 4, "revenue_wape_pct": 8.3, "op_wape_pct": 129.2, "n": 4, "note": "단일 회사 4분기 — 통계 아님", "driver_at_freeze": "customer_yard_revenue_weighted", "frozen_inputs": "fin(연결/별도)·고객 조선사 모델·지주 자회사 모델은 2025Q2 까지의 분기만; 선표는 체결일 ≤ 2025Q2 말일 계약(원장 최신 금액·코호트 등급, 환산 없음); 잔고는 yards_cache 2025Q2; 시세·환율 forward·prices 미사용. 고객 가중치(suppliers.json 언급 비중)와 합병 체인링크는 현재 지식", "detail": [{"q": "2025Q3", "rev_pred": 277.78, "rev_act": 285.56, "op_pred": -13.37, "op_act": -50.22}, {"q": "2025Q4", "rev_pred": 411.63, "rev_act": 490.43, "op_pred": -19.81, "op_act": 49.97}, {"q": "2026Q1", "rev_pred": 341.66, "rev_act": 319.14, "op_pred": -16.44, "op_act": 5.34}, {"q": "2026Q2", "rev_pred": 355.91, "rev_act": 367.92, "op_pred": -17.13, "op_act": 31.44}]}</t>
+          <t>백테스트: {"freeze": "2025Q2", "horizon": 4, "revenue_wape_pct": 8.3, "op_wape_pct": 129.2, "n": 4, "note": "단일 회사 4분기 — 통계 아님", "driver_at_freeze": "customer_yard_revenue_weighted", "selection_oos_at_freeze": {"freeze": "2024Q2", "n": 4, "wape_link": 22.2, "wape_trend": 23.0, "adopted": true}, "frozen_inputs": "fin(연결/별도)·고객 조선사 모델·지주 자회사 모델은 2025Q2 까지의 분기만; 선표는 체결일 ≤ 2025Q2 말일 계약(원장 최신 금액·코호트 등급, 환산 없음); 잔고는 yards_cache 2025Q2; 시세·환율 forward·prices·forecast_panel 신규수주 미사용. 고객 가중치(suppliers.json 언급 비중)와 합병 체인링크는 현재 지식; 고객 연동 채택은 동결 모델 안에서도 자기 la−4분기 OOS 규칙(selection_oos_at_freeze)", "detail": [{"q": "2025Q3", "rev_pred": 277.78, "rev_act": 285.56, "op_pred": -13.37, "op_act": -50.22}, {"q": "2025Q4", "rev_pred": 411.63, "rev_act": 490.43, "op_pred": -19.81, "op_act": 49.97}, {"q": "2026Q1", "rev_pred": 341.66, "rev_act": 319.14, "op_pred": -16.44, "op_act": 5.34}, {"q": "2026Q2", "rev_pred": 355.91, "rev_act": 367.92, "op_pred": -17.13, "op_act": 31.44}]}</t>
         </is>
       </c>
     </row>
@@ -6410,36 +6386,36 @@
         <v/>
       </c>
       <c r="AC21" s="24" t="n">
-        <v>0.094495</v>
+        <v>0.3023</v>
       </c>
       <c r="AD21" s="24" t="n">
-        <v>-0.01702</v>
+        <v>0.302293</v>
       </c>
       <c r="AE21" s="25" t="n"/>
       <c r="AF21" s="24" t="n">
-        <v>0.153275</v>
+        <v>0.302299</v>
       </c>
       <c r="AG21" s="24" t="n">
-        <v>0.102845</v>
+        <v>0.30229</v>
       </c>
       <c r="AH21" s="24" t="n">
-        <v>0.182633</v>
+        <v>0.151151</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.228199</v>
+        <v>0.151156</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>0.229609</v>
+        <v>0.151148</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>0.138579</v>
+        <v>0.151146</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>0.075131</v>
+        <v>0.075568</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>0.014187</v>
+        <v>0.075569</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -6556,42 +6532,42 @@
         <v/>
       </c>
       <c r="AC22" s="24" t="n">
-        <v>0.161931</v>
+        <v>0.161934</v>
       </c>
       <c r="AD22" s="24" t="n">
-        <v>0.161923</v>
+        <v>0.161928</v>
       </c>
       <c r="AE22" s="25">
         <f>IFERROR(subQ!AE8/subQ!AE5,"")</f>
         <v/>
       </c>
       <c r="AF22" s="24" t="n">
-        <v>0.16193</v>
+        <v>0.161927</v>
       </c>
       <c r="AG22" s="24" t="n">
-        <v>0.161918</v>
+        <v>0.161936</v>
       </c>
       <c r="AH22" s="24" t="n">
-        <v>0.161923</v>
+        <v>0.161929</v>
       </c>
       <c r="AI22" s="24" t="n">
-        <v>0.161918</v>
+        <v>0.161924</v>
       </c>
       <c r="AJ22" s="25">
         <f>IFERROR(subQ!AJ8/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK22" s="24" t="n">
-        <v>0.16192</v>
+        <v>0.161922</v>
       </c>
       <c r="AL22" s="24" t="n">
-        <v>0.16193</v>
+        <v>0.161923</v>
       </c>
       <c r="AM22" s="24" t="n">
         <v>0.161932</v>
       </c>
       <c r="AN22" s="24" t="n">
-        <v>0.161918</v>
+        <v>0.161929</v>
       </c>
       <c r="AO22" s="25">
         <f>IFERROR(subQ!AO8/subQ!AO5,"")</f>
@@ -6711,42 +6687,42 @@
         <v/>
       </c>
       <c r="AC23" s="24" t="n">
-        <v>-0.014046</v>
+        <v>-0.014064</v>
       </c>
       <c r="AD23" s="24" t="n">
-        <v>-0.014064</v>
+        <v>-0.01406</v>
       </c>
       <c r="AE23" s="25">
         <f>IFERROR(subQ!AE9/subQ!AE5,"")</f>
         <v/>
       </c>
       <c r="AF23" s="24" t="n">
-        <v>-0.014074</v>
+        <v>-0.014051</v>
       </c>
       <c r="AG23" s="24" t="n">
-        <v>-0.014072</v>
+        <v>-0.014067</v>
       </c>
       <c r="AH23" s="24" t="n">
-        <v>-0.014069</v>
+        <v>-0.014062</v>
       </c>
       <c r="AI23" s="24" t="n">
-        <v>-0.014069</v>
+        <v>-0.014064</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>-0.014053</v>
+        <v>-0.014067</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>-0.01407</v>
+        <v>-0.014069</v>
       </c>
       <c r="AM23" s="24" t="n">
-        <v>-0.014067</v>
+        <v>-0.014052</v>
       </c>
       <c r="AN23" s="24" t="n">
-        <v>-0.014055</v>
+        <v>-0.014062</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -6995,32 +6971,32 @@
         <v/>
       </c>
       <c r="AF25" s="29" t="n">
-        <v>5.9</v>
+        <v>5.87</v>
       </c>
       <c r="AG25" s="29" t="n">
-        <v>5.9</v>
+        <v>5.87</v>
       </c>
       <c r="AH25" s="29" t="n">
-        <v>5.9</v>
+        <v>5.86</v>
       </c>
       <c r="AI25" s="29" t="n">
-        <v>5.9</v>
+        <v>5.86</v>
       </c>
       <c r="AJ25" s="30">
         <f>subQ!AJ11</f>
         <v/>
       </c>
       <c r="AK25" s="29" t="n">
-        <v>5.88</v>
+        <v>5.83</v>
       </c>
       <c r="AL25" s="29" t="n">
-        <v>5.88</v>
+        <v>5.82</v>
       </c>
       <c r="AM25" s="29" t="n">
-        <v>5.87</v>
+        <v>5.8</v>
       </c>
       <c r="AN25" s="29" t="n">
-        <v>5.87</v>
+        <v>5.79</v>
       </c>
       <c r="AO25" s="30">
         <f>subQ!AO11</f>
@@ -7450,7 +7426,7 @@
         <v/>
       </c>
       <c r="AC28" s="24" t="n">
-        <v>0.053333</v>
+        <v>0.045455</v>
       </c>
       <c r="AD28" s="24" t="n">
         <v>-0</v>
@@ -7460,13 +7436,13 @@
         <v/>
       </c>
       <c r="AF28" s="24" t="n">
-        <v>0.055556</v>
+        <v>0</v>
       </c>
       <c r="AG28" s="24" t="n">
-        <v>0.05</v>
+        <v>-0</v>
       </c>
       <c r="AH28" s="24" t="n">
-        <v>0.057143</v>
+        <v>-0</v>
       </c>
       <c r="AI28" s="24" t="n">
         <v>-0</v>
@@ -7482,7 +7458,7 @@
         <v>-0</v>
       </c>
       <c r="AM28" s="24" t="n">
-        <v>0.035714</v>
+        <v>-0</v>
       </c>
       <c r="AN28" s="24" t="n">
         <v>-0</v>
@@ -7969,10 +7945,10 @@
         <v/>
       </c>
       <c r="AC32" s="29" t="n">
-        <v>-0.0035</v>
+        <v>0.0065</v>
       </c>
       <c r="AD32" s="29" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE32" s="30" t="n"/>
       <c r="AF32" s="29" t="n">
@@ -7985,11 +7961,11 @@
         <v>0</v>
       </c>
       <c r="AI32" s="29" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AJ32" s="30" t="n"/>
       <c r="AK32" s="29" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL32" s="29" t="n">
         <v>0.6899999999999999</v>
@@ -7998,7 +7974,7 @@
         <v>0</v>
       </c>
       <c r="AN32" s="29" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="AO32" s="30" t="n"/>
     </row>
@@ -8100,30 +8076,30 @@
         <v>0.001</v>
       </c>
       <c r="AD33" s="29" t="n">
-        <v>-0</v>
+        <v>0.01</v>
       </c>
       <c r="AE33" s="30" t="n"/>
       <c r="AF33" s="29" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="AG33" s="29" t="n">
         <v>0.7</v>
       </c>
       <c r="AH33" s="29" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AI33" s="29" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="AJ33" s="30" t="n"/>
       <c r="AK33" s="29" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="AL33" s="29" t="n">
-        <v>0.7</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AM33" s="29" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="AN33" s="29" t="n">
         <v>0</v>
@@ -8441,36 +8417,36 @@
         <v/>
       </c>
       <c r="AC36" s="24" t="n">
-        <v>0.001826</v>
+        <v>0.000806</v>
       </c>
       <c r="AD36" s="24" t="n">
-        <v>-0.001121</v>
+        <v>-0.003974</v>
       </c>
       <c r="AE36" s="25" t="n"/>
       <c r="AF36" s="24" t="n">
-        <v>0.000877</v>
+        <v>3.9e-05</v>
       </c>
       <c r="AG36" s="24" t="n">
-        <v>-0.0006579999999999999</v>
+        <v>-0.002021</v>
       </c>
       <c r="AH36" s="24" t="n">
-        <v>0.000851</v>
+        <v>-0.000208</v>
       </c>
       <c r="AI36" s="24" t="n">
-        <v>-0.003119</v>
+        <v>-0.005816</v>
       </c>
       <c r="AJ36" s="25" t="n"/>
       <c r="AK36" s="24" t="n">
-        <v>-0.000621</v>
+        <v>-0.001175</v>
       </c>
       <c r="AL36" s="24" t="n">
-        <v>-0.001695</v>
+        <v>-0.003438</v>
       </c>
       <c r="AM36" s="24" t="n">
-        <v>0.00035</v>
+        <v>-0.000892</v>
       </c>
       <c r="AN36" s="24" t="n">
-        <v>-0.003343</v>
+        <v>-0.006986</v>
       </c>
       <c r="AO36" s="25" t="n"/>
     </row>
@@ -9102,12 +9078,8 @@
       <c r="AD42" s="31" t="n"/>
       <c r="AE42" s="25" t="n"/>
       <c r="AF42" s="31" t="n"/>
-      <c r="AG42" s="24" t="n">
-        <v>20.156757</v>
-      </c>
-      <c r="AH42" s="24" t="n">
-        <v>62.294078</v>
-      </c>
+      <c r="AG42" s="31" t="n"/>
+      <c r="AH42" s="31" t="n"/>
       <c r="AI42" s="31" t="n"/>
       <c r="AJ42" s="25" t="n"/>
       <c r="AK42" s="31" t="n"/>
@@ -9503,42 +9475,42 @@
         <v/>
       </c>
       <c r="AC45" s="24" t="n">
-        <v>-0.014046</v>
+        <v>-0.014064</v>
       </c>
       <c r="AD45" s="24" t="n">
-        <v>-0.014064</v>
+        <v>-0.01406</v>
       </c>
       <c r="AE45" s="25">
         <f>IFERROR(subQ!AE36/subQ!AE35,"")</f>
         <v/>
       </c>
       <c r="AF45" s="24" t="n">
-        <v>-0.014074</v>
+        <v>-0.014051</v>
       </c>
       <c r="AG45" s="24" t="n">
-        <v>-0.014072</v>
+        <v>-0.014067</v>
       </c>
       <c r="AH45" s="24" t="n">
-        <v>-0.014069</v>
+        <v>-0.014062</v>
       </c>
       <c r="AI45" s="24" t="n">
-        <v>-0.014069</v>
+        <v>-0.014064</v>
       </c>
       <c r="AJ45" s="25">
         <f>IFERROR(subQ!AJ36/subQ!AJ35,"")</f>
         <v/>
       </c>
       <c r="AK45" s="24" t="n">
-        <v>-0.014053</v>
+        <v>-0.014067</v>
       </c>
       <c r="AL45" s="24" t="n">
-        <v>-0.01407</v>
+        <v>-0.014069</v>
       </c>
       <c r="AM45" s="24" t="n">
-        <v>-0.014067</v>
+        <v>-0.014052</v>
       </c>
       <c r="AN45" s="24" t="n">
-        <v>-0.014055</v>
+        <v>-0.014062</v>
       </c>
       <c r="AO45" s="25">
         <f>IFERROR(subQ!AO36/subQ!AO35,"")</f>
@@ -10279,7 +10251,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-09-30</t>
+          <t>UPDATE: 26-10-02</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -19016,7 +18988,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-09-30</t>
+          <t>UPDATE: 26-10-02</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -31990,26 +31962,20 @@
         <v>20.35</v>
       </c>
       <c r="AC33" s="20" t="n">
-        <v>14.69</v>
+        <v>14.98</v>
       </c>
       <c r="AD33" s="20" t="n">
-        <v>15.45</v>
+        <v>16.73</v>
       </c>
       <c r="AE33" s="35">
         <f>SUM(AA33:AD33)</f>
         <v/>
       </c>
       <c r="AF33" s="20" t="n">
-        <v>16.33</v>
-      </c>
-      <c r="AG33" s="20">
-        <f>IFERROR(AB33*(1+변수!AG42),"")</f>
-        <v/>
-      </c>
-      <c r="AH33" s="20">
-        <f>IFERROR(AC33*(1+변수!AH42),"")</f>
-        <v/>
-      </c>
+        <v>18.11</v>
+      </c>
+      <c r="AG33" s="20" t="n"/>
+      <c r="AH33" s="20" t="n"/>
       <c r="AI33" s="20" t="n"/>
       <c r="AJ33" s="35">
         <f>SUM(AF33:AI33)</f>
@@ -40459,7 +40425,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>20.3</v>
+        <v>-47.4</v>
       </c>
     </row>
     <row r="30">
@@ -40478,9 +40444,6 @@
           <t>per_now</t>
         </is>
       </c>
-      <c r="D31" t="n">
-        <v>430.54</v>
-      </c>
     </row>
     <row r="32">
       <c r="C32" s="2" t="inlineStr">
@@ -40499,7 +40462,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.0008</v>
+        <v>-0.002</v>
       </c>
     </row>
     <row r="34">
@@ -40508,18 +40471,12 @@
           <t>fair_pbr</t>
         </is>
       </c>
-      <c r="D34" t="n">
-        <v>0.01</v>
-      </c>
     </row>
     <row r="35">
       <c r="C35" s="2" t="inlineStr">
         <is>
           <t>fair_value_pbr</t>
         </is>
-      </c>
-      <c r="D35" t="n">
-        <v>200</v>
       </c>
     </row>
     <row r="36">

--- a/argus/kship/models/085310_model.xlsx
+++ b/argus/kship/models/085310_model.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="변수" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="subQ" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="분기" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TP" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="외화" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="변수" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="subQ" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="분기" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="TP" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="외화" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="변수H">변수!$C$1:$AO$1</definedName>
@@ -3922,7 +3922,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-05</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-06</t>
         </is>
       </c>
     </row>
@@ -4793,35 +4793,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1354.78</v>
+        <v>1351.18</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1460.21</v>
+        <v>1459.61</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -4912,35 +4912,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5031,35 +5031,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>858.4</v>
+        <v>855.39</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>921.0599999999999</v>
+        <v>920.6900000000001</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5150,35 +5150,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5269,35 +5269,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1525.7</v>
+        <v>1519.07</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1694.79</v>
+        <v>1693.81</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5388,35 +5388,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5507,35 +5507,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>202.07</v>
+        <v>201.53</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>214.1</v>
+        <v>214.03</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5626,35 +5626,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -5761,7 +5761,7 @@
         <v>8930</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>8940</v>
+        <v>8800</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -5943,7 +5943,7 @@
         <v>6950</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>8750</v>
+        <v>8650</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -6034,7 +6034,7 @@
         <v>8774.700000000001</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>8925</v>
+        <v>8883.299999999999</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -8741,7 +8741,7 @@
         </is>
       </c>
       <c r="D42" s="34" t="n">
-        <v>8940</v>
+        <v>8800</v>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
@@ -8781,7 +8781,7 @@
       </c>
       <c r="D43" s="35" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261006</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -9607,7 +9607,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-05</t>
+          <t>UPDATE: 26-10-06</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -18523,7 +18523,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-05</t>
+          <t>UPDATE: 26-10-06</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -33183,7 +33183,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261006</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -38188,7 +38188,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261006</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -40291,7 +40291,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.37</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/085310_model.xlsx
+++ b/argus/kship/models/085310_model.xlsx
@@ -3922,7 +3922,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-06</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-07</t>
         </is>
       </c>
     </row>
@@ -4793,35 +4793,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1351.18</v>
+        <v>1348.08</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1459.61</v>
+        <v>1458.99</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -4912,35 +4912,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5031,35 +5031,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>855.39</v>
+        <v>853.26</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>920.6900000000001</v>
+        <v>920.3099999999999</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5150,35 +5150,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5269,35 +5269,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1519.07</v>
+        <v>1516.47</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1693.81</v>
+        <v>1692.86</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5388,35 +5388,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5507,35 +5507,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>201.53</v>
+        <v>201.07</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>214.03</v>
+        <v>213.96</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5626,35 +5626,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -5761,7 +5761,7 @@
         <v>8930</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>8800</v>
+        <v>8850</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6034,7 +6034,7 @@
         <v>8774.700000000001</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>8883.299999999999</v>
+        <v>8887.5</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -8741,11 +8741,11 @@
         </is>
       </c>
       <c r="D42" s="34" t="n">
-        <v>8800</v>
+        <v>8850</v>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 8,940원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 8,870원)</t>
         </is>
       </c>
       <c r="F42" s="9" t="n"/>
@@ -8781,7 +8781,7 @@
       </c>
       <c r="D43" s="35" t="inlineStr">
         <is>
-          <t>20261006</t>
+          <t>20261007</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -9607,7 +9607,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-06</t>
+          <t>UPDATE: 26-10-07</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -18523,7 +18523,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-06</t>
+          <t>UPDATE: 26-10-07</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -33183,7 +33183,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261006</t>
+          <t>20261007</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -38188,7 +38188,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261006</t>
+          <t>20261007</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/085310_model.xlsx
+++ b/argus/kship/models/085310_model.xlsx
@@ -3922,7 +3922,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-07</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-08</t>
         </is>
       </c>
     </row>
@@ -9607,7 +9607,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-07</t>
+          <t>UPDATE: 26-10-08</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -18523,7 +18523,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-07</t>
+          <t>UPDATE: 26-10-08</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/085310_model.xlsx
+++ b/argus/kship/models/085310_model.xlsx
@@ -4793,35 +4793,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1348.08</v>
+        <v>1346.2</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1458.99</v>
+        <v>1458.38</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -4912,35 +4912,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5031,35 +5031,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>853.26</v>
+        <v>851.8099999999999</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>920.3099999999999</v>
+        <v>919.9299999999999</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5150,35 +5150,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5269,35 +5269,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1516.47</v>
+        <v>1512.43</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1692.86</v>
+        <v>1691.86</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5388,35 +5388,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5507,35 +5507,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>201.07</v>
+        <v>200.79</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.96</v>
+        <v>213.89</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5626,35 +5626,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -5761,7 +5761,7 @@
         <v>8930</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>8850</v>
+        <v>8780</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -5943,7 +5943,7 @@
         <v>6950</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>8650</v>
+        <v>8600</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -6034,7 +6034,7 @@
         <v>8774.700000000001</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>8887.5</v>
+        <v>8894</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -8741,11 +8741,11 @@
         </is>
       </c>
       <c r="D42" s="34" t="n">
-        <v>8850</v>
+        <v>8780</v>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 8,870원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 8,850원)</t>
         </is>
       </c>
       <c r="F42" s="9" t="n"/>
@@ -8781,7 +8781,7 @@
       </c>
       <c r="D43" s="35" t="inlineStr">
         <is>
-          <t>20261007</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -33183,7 +33183,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261007</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -38188,7 +38188,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261007</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/085310_model.xlsx
+++ b/argus/kship/models/085310_model.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="변수" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="subQ" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="분기" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="TP" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="외화" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="변수" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="subQ" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="분기" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TP" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="외화" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="변수H">변수!$C$1:$AO$1</definedName>
@@ -1557,19 +1557,19 @@
     <comment ref="AD39" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-직전 결산 DPS 10원 유지</t>
+직전 결산 DPS 100원(fin 10원 ÷ 1/10 병합/분할 환산) 유지</t>
       </text>
     </comment>
     <comment ref="AI39" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-직전 결산 DPS 10원 유지</t>
+직전 결산 DPS 100원(fin 10원 ÷ 1/10 병합/분할 환산) 유지</t>
       </text>
     </comment>
     <comment ref="AN39" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-직전 결산 DPS 10원 유지</t>
+직전 결산 DPS 100원(fin 10원 ÷ 1/10 병합/분할 환산) 유지</t>
       </text>
     </comment>
   </commentList>
@@ -1968,37 +1968,37 @@
     </comment>
     <comment ref="AH11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 770억 × 3.04%(CF 이자수취 ÷ 평균 이자발생자산(2025Q3~2026Q2; 주석 이자수익 0분기 &lt; 4)) − 총차입금 172억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 764억 × 3.04%(CF 이자수취 ÷ 평균 이자발생자산(2025Q3~2026Q2; 주석 이자수익 0분기 &lt; 4)) − 총차입금 172억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AI11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 770억 × 3.04%(CF 이자수취 ÷ 평균 이자발생자산(2025Q3~2026Q2; 주석 이자수익 0분기 &lt; 4)) − 총차입금 172억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 764억 × 3.04%(CF 이자수취 ÷ 평균 이자발생자산(2025Q3~2026Q2; 주석 이자수익 0분기 &lt; 4)) − 총차입금 172억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AK11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 766억 × 3.04%(CF 이자수취 ÷ 평균 이자발생자산(2025Q3~2026Q2; 주석 이자수익 0분기 &lt; 4)) − 총차입금 172억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 759억 × 3.04%(CF 이자수취 ÷ 평균 이자발생자산(2025Q3~2026Q2; 주석 이자수익 0분기 &lt; 4)) − 총차입금 172억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AL11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 765억 × 3.04%(CF 이자수취 ÷ 평균 이자발생자산(2025Q3~2026Q2; 주석 이자수익 0분기 &lt; 4)) − 총차입금 172억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 758억 × 3.04%(CF 이자수취 ÷ 평균 이자발생자산(2025Q3~2026Q2; 주석 이자수익 0분기 &lt; 4)) − 총차입금 172억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AM11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 762억 × 3.04%(CF 이자수취 ÷ 평균 이자발생자산(2025Q3~2026Q2; 주석 이자수익 0분기 &lt; 4)) − 총차입금 172억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 750억 × 3.04%(CF 이자수취 ÷ 평균 이자발생자산(2025Q3~2026Q2; 주석 이자수익 0분기 &lt; 4)) − 총차입금 172억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AN11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 762억 × 3.04%(CF 이자수취 ÷ 평균 이자발생자산(2025Q3~2026Q2; 주석 이자수익 0분기 &lt; 4)) − 총차입금 172억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 749억 × 3.04%(CF 이자수취 ÷ 평균 이자발생자산(2025Q3~2026Q2; 주석 이자수익 0분기 &lt; 4)) − 총차입금 172억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
@@ -2028,37 +2028,37 @@
     </comment>
     <comment ref="AH12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 770억 × 3.04%(CF 이자수취 ÷ 평균 이자발생자산(2025Q3~2026Q2; 주석 이자수익 0분기 &lt; 4)) − 총차입금 172억 × 0.00%(없음) (연율) ÷ 4
+        <t>추정: 이자발생자산 764억 × 3.04%(CF 이자수취 ÷ 평균 이자발생자산(2025Q3~2026Q2; 주석 이자수익 0분기 &lt; 4)) − 총차입금 172억 × 0.00%(없음) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AI12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 770억 × 3.04%(CF 이자수취 ÷ 평균 이자발생자산(2025Q3~2026Q2; 주석 이자수익 0분기 &lt; 4)) − 총차입금 172억 × 0.00%(없음) (연율) ÷ 4
+        <t>추정: 이자발생자산 764억 × 3.04%(CF 이자수취 ÷ 평균 이자발생자산(2025Q3~2026Q2; 주석 이자수익 0분기 &lt; 4)) − 총차입금 172억 × 0.00%(없음) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AK12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 766억 × 3.04%(CF 이자수취 ÷ 평균 이자발생자산(2025Q3~2026Q2; 주석 이자수익 0분기 &lt; 4)) − 총차입금 172억 × 0.00%(없음) (연율) ÷ 4
+        <t>추정: 이자발생자산 759억 × 3.04%(CF 이자수취 ÷ 평균 이자발생자산(2025Q3~2026Q2; 주석 이자수익 0분기 &lt; 4)) − 총차입금 172억 × 0.00%(없음) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AL12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 765억 × 3.04%(CF 이자수취 ÷ 평균 이자발생자산(2025Q3~2026Q2; 주석 이자수익 0분기 &lt; 4)) − 총차입금 172억 × 0.00%(없음) (연율) ÷ 4
+        <t>추정: 이자발생자산 758억 × 3.04%(CF 이자수취 ÷ 평균 이자발생자산(2025Q3~2026Q2; 주석 이자수익 0분기 &lt; 4)) − 총차입금 172억 × 0.00%(없음) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AM12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 762억 × 3.04%(CF 이자수취 ÷ 평균 이자발생자산(2025Q3~2026Q2; 주석 이자수익 0분기 &lt; 4)) − 총차입금 172억 × 0.00%(없음) (연율) ÷ 4
+        <t>추정: 이자발생자산 750억 × 3.04%(CF 이자수취 ÷ 평균 이자발생자산(2025Q3~2026Q2; 주석 이자수익 0분기 &lt; 4)) − 총차입금 172억 × 0.00%(없음) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AN12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 762억 × 3.04%(CF 이자수취 ÷ 평균 이자발생자산(2025Q3~2026Q2; 주석 이자수익 0분기 &lt; 4)) − 총차입금 172억 × 0.00%(없음) (연율) ÷ 4
+        <t>추정: 이자발생자산 749억 × 3.04%(CF 이자수취 ÷ 평균 이자발생자산(2025Q3~2026Q2; 주석 이자수익 0분기 &lt; 4)) − 총차입금 172억 × 0.00%(없음) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
@@ -2904,92 +2904,92 @@
     </comment>
     <comment ref="E30" authorId="0" shapeId="0">
       <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — fin.shares.common_outstanding</t>
+        <t>추정(실적 구간 갭필): fin.shares.common_outstanding 78,880,322주 × 1/10(환산 — 2026Q2 1/10 병합; IAS 33.64 비교표시·수정주가 이력과 정합)</t>
       </text>
     </comment>
     <comment ref="G30" authorId="0" shapeId="0">
       <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — fin.shares.common_outstanding</t>
+        <t>추정(실적 구간 갭필): fin.shares.common_outstanding 78,880,322주 × 1/10(환산 — 2026Q2 1/10 병합; IAS 33.64 비교표시·수정주가 이력과 정합)</t>
       </text>
     </comment>
     <comment ref="H30" authorId="0" shapeId="0">
       <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — fin.shares.common_outstanding</t>
+        <t>추정(실적 구간 갭필): fin.shares.common_outstanding 78,880,322주 × 1/10(환산 — 2026Q2 1/10 병합; IAS 33.64 비교표시·수정주가 이력과 정합)</t>
       </text>
     </comment>
     <comment ref="I30" authorId="0" shapeId="0">
       <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — fin.shares.common_outstanding</t>
+        <t>추정(실적 구간 갭필): fin.shares.common_outstanding 78,880,322주 × 1/10(환산 — 2026Q2 1/10 병합; IAS 33.64 비교표시·수정주가 이력과 정합)</t>
       </text>
     </comment>
     <comment ref="J30" authorId="0" shapeId="0">
       <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — fin.shares.common_outstanding</t>
+        <t>추정(실적 구간 갭필): fin.shares.common_outstanding 78,880,322주 × 1/10(환산 — 2026Q2 1/10 병합; IAS 33.64 비교표시·수정주가 이력과 정합)</t>
       </text>
     </comment>
     <comment ref="L30" authorId="0" shapeId="0">
       <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — fin.shares.common_outstanding</t>
+        <t>추정(실적 구간 갭필): fin.shares.common_outstanding 78,880,322주 × 1/10(환산 — 2026Q2 1/10 병합; IAS 33.64 비교표시·수정주가 이력과 정합)</t>
       </text>
     </comment>
     <comment ref="M30" authorId="0" shapeId="0">
       <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — fin.shares.common_outstanding</t>
+        <t>추정(실적 구간 갭필): fin.shares.common_outstanding 78,880,322주 × 1/10(환산 — 2026Q2 1/10 병합; IAS 33.64 비교표시·수정주가 이력과 정합)</t>
       </text>
     </comment>
     <comment ref="N30" authorId="0" shapeId="0">
       <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — fin.shares.common_outstanding</t>
+        <t>추정(실적 구간 갭필): fin.shares.common_outstanding 78,880,322주 × 1/10(환산 — 2026Q2 1/10 병합; IAS 33.64 비교표시·수정주가 이력과 정합)</t>
       </text>
     </comment>
     <comment ref="O30" authorId="0" shapeId="0">
       <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — fin.shares.common_outstanding</t>
+        <t>추정(실적 구간 갭필): fin.shares.common_outstanding 78,880,322주 × 1/10(환산 — 2026Q2 1/10 병합; IAS 33.64 비교표시·수정주가 이력과 정합)</t>
       </text>
     </comment>
     <comment ref="Q30" authorId="0" shapeId="0">
       <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — fin.shares.common_outstanding</t>
+        <t>추정(실적 구간 갭필): fin.shares.common_outstanding 78,880,322주 × 1/10(환산 — 2026Q2 1/10 병합; IAS 33.64 비교표시·수정주가 이력과 정합)</t>
       </text>
     </comment>
     <comment ref="R30" authorId="0" shapeId="0">
       <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — fin.shares.common_outstanding</t>
+        <t>추정(실적 구간 갭필): fin.shares.common_outstanding 78,880,322주 × 1/10(환산 — 2026Q2 1/10 병합; IAS 33.64 비교표시·수정주가 이력과 정합)</t>
       </text>
     </comment>
     <comment ref="S30" authorId="0" shapeId="0">
       <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — fin.shares.common_outstanding</t>
+        <t>추정(실적 구간 갭필): fin.shares.common_outstanding 78,880,322주 × 1/10(환산 — 2026Q2 1/10 병합; IAS 33.64 비교표시·수정주가 이력과 정합)</t>
       </text>
     </comment>
     <comment ref="T30" authorId="0" shapeId="0">
       <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — fin.shares.common_outstanding</t>
+        <t>추정(실적 구간 갭필): fin.shares.common_outstanding 78,630,845주 × 1/10(환산 — 2026Q2 1/10 병합; IAS 33.64 비교표시·수정주가 이력과 정합)</t>
       </text>
     </comment>
     <comment ref="V30" authorId="0" shapeId="0">
       <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — fin.shares.common_outstanding</t>
+        <t>추정(실적 구간 갭필): fin.shares.common_outstanding 75,678,505주 × 1/10(환산 — 2026Q2 1/10 병합; IAS 33.64 비교표시·수정주가 이력과 정합)</t>
       </text>
     </comment>
     <comment ref="W30" authorId="0" shapeId="0">
       <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — fin.shares.common_outstanding</t>
+        <t>추정(실적 구간 갭필): fin.shares.common_outstanding 69,497,113주 × 1/10(환산 — 2026Q2 1/10 병합; IAS 33.64 비교표시·수정주가 이력과 정합)</t>
       </text>
     </comment>
     <comment ref="X30" authorId="0" shapeId="0">
       <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — fin.shares.common_outstanding</t>
+        <t>추정(실적 구간 갭필): fin.shares.common_outstanding 69,497,113주 × 1/10(환산 — 2026Q2 1/10 병합; IAS 33.64 비교표시·수정주가 이력과 정합)</t>
       </text>
     </comment>
     <comment ref="Y30" authorId="0" shapeId="0">
       <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — fin.shares.common_outstanding</t>
+        <t>추정(실적 구간 갭필): fin.shares.common_outstanding 69,481,164주 × 1/10(환산 — 2026Q2 1/10 병합; IAS 33.64 비교표시·수정주가 이력과 정합)</t>
       </text>
     </comment>
     <comment ref="AA30" authorId="0" shapeId="0">
       <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — fin.shares.common_outstanding</t>
+        <t>추정(실적 구간 갭필): fin.shares.common_outstanding 69,481,164주 × 1/10(환산 — 2026Q2 1/10 병합; IAS 33.64 비교표시·수정주가 이력과 정합)</t>
       </text>
     </comment>
     <comment ref="AB30" authorId="0" shapeId="0">
@@ -3199,29 +3199,29 @@
     </comment>
     <comment ref="T33" authorId="0" shapeId="0">
       <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — fin.dividend.dps_common(연간, Q4 에 표기)</t>
+        <t>추정(실적 구간 갭필): fin.dividend.dps_common 10원 ÷ 1/10(병합/분할 환산 — 2026Q2 1/10 병합)</t>
       </text>
     </comment>
     <comment ref="Y33" authorId="0" shapeId="0">
       <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — fin.dividend.dps_common(연간, Q4 에 표기)</t>
+        <t>추정(실적 구간 갭필): fin.dividend.dps_common 10원 ÷ 1/10(병합/분할 환산 — 2026Q2 1/10 병합)</t>
       </text>
     </comment>
     <comment ref="AD33" authorId="0" shapeId="0">
       <text>
-        <t>추정: 직전 결산 DPS 10원 유지
+        <t>추정: 직전 결산 DPS 100원(fin 10원 ÷ 1/10 병합/분할 환산) 유지
 [abs]</t>
       </text>
     </comment>
     <comment ref="AI33" authorId="0" shapeId="0">
       <text>
-        <t>추정: 직전 결산 DPS 10원 유지
+        <t>추정: 직전 결산 DPS 100원(fin 10원 ÷ 1/10 병합/분할 환산) 유지
 [abs]</t>
       </text>
     </comment>
     <comment ref="AN33" authorId="0" shapeId="0">
       <text>
-        <t>추정: 직전 결산 DPS 10원 유지
+        <t>추정: 직전 결산 DPS 100원(fin 10원 ÷ 1/10 병합/분할 환산) 유지
 [abs]</t>
       </text>
     </comment>
@@ -3922,7 +3922,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-08</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-09</t>
         </is>
       </c>
     </row>
@@ -4092,7 +4092,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>· 밸류에이션 — PER 밴드 10.0/15.0/20.0배(sector_default(레퍼런스 TP_PE PB 예시 10/15/20배; 과거 PER 중위 36.1배가 캡 5~30 밖 — 턴어라운드 초기 TTM EPS 왜곡)) · COE 9.0% · 12M fwd EPS 가중 0.5(가정). 모델 산출값 구간이며 추천이 아니다</t>
+          <t>· 밸류에이션 — PER 밴드 5.0/5.4/6.8배(hist_quarterly(분기 평균가 ÷ TTM EPS, 10분기, 25/50/75 백분위) · 캡 5~30배 적용(원값 1.3/5.4/6.8)) · COE 9.0% · 12M fwd EPS 가중 0.5(가정). 모델 산출값 구간이며 추천이 아니다</t>
         </is>
       </c>
     </row>
@@ -4123,14 +4123,14 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>한계: 모델 quality.warnings — 매출 드라이버 폴백(고객 연동 OOS 기각 — 동결 2025Q2 이후 4분기 매출 WAPE 연동 8.3% &gt; 추세 6.6% × 1.10 (suppliers_mentions·시차 4·4분기 이동합·창 12, r=0.96 유의)): 전년동기 × (1+g) 추세 / 감가상각비가 face·CF 에 없음(주석 미파싱) → EBITDA·EV/EBITDA 미산출</t>
+          <t>한계: 모델 quality.warnings — 매출 드라이버 폴백(고객 연동 OOS 기각 — 동결 2025Q2 이후 4분기 매출 WAPE 연동 8.3% &gt; 추세 6.6% × 1.10 (suppliers_mentions·시차 4·4분기 이동합·창 12, r=0.96 유의)): 전년동기 × (1+g) 추세 / 주식수 사건 환산: 2026Q2 1/10 병합(eps_reported 교차검증 confirmed) → 사건 전 실적 18분기의 주식수·EPS·BPS·DPS 를 비율 환산(IAS 33.64; 셀 kind estimate, basis 에 원주식수·비율) / 감가상각비가 face·CF 에 없음(주석 미파싱) → EBITDA·EV/EBITDA 미산출</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>백테스트: {"freeze": "2025Q2", "horizon": 4, "revenue_wape_pct": 8.3, "op_wape_pct": 129.2, "n": 4, "note": "단일 회사 4분기 — 통계 아님", "driver_at_freeze": "customer_yard_revenue_weighted", "selection_oos_at_freeze": {"freeze": "2024Q2", "n": 4, "wape_link": 11.6, "wape_trend": 23.0, "adopted": true, "decision": "adopted"}, "frozen_inputs": "fin(연결/별도)·고객 조선사 모델·지주 자회사 모델은 2025Q2 까지의 분기만; 선표는 체결일 ≤ 2025Q2 말일 계약(원장 최신 금액·코호트 등급, 환산 없음); 잔고는 yards_cache 2025Q2; 시세·환율 forward·prices·forecast_panel 신규수주 미사용. 고객 가중치(suppliers.json 언급 비중)와 합병 체인링크는 현재 지식; 고객 연동 채택은 동결 모델 안에서도 자기 la−4분기 OOS 규칙(selection_oos_at_freeze)", "detail": [{"q": "2025Q3", "rev_pred": 277.78, "rev_act": 285.56, "op_pred": -13.37, "op_act": -50.22}, {"q": "2025Q4", "rev_pred": 411.63, "rev_act": 490.43, "op_pred": -19.81, "op_act": 49.97}, {"q": "2026Q1", "rev_pred": 341.66, "rev_act": 319.14, "op_pred": -16.44, "op_act": 5.34}, {"q": "2026Q2", "rev_pred": 355.91, "rev_act": 367.92, "op_pred": -17.13, "op_act": 31.44}]}</t>
+          <t>백테스트: {"freeze": "2025Q2", "horizon": 4, "revenue_wape_pct": 8.3, "op_wape_pct": 129.2, "n": 4, "note": "단일 회사 4분기 — 통계 아님", "driver_at_freeze": "customer_yard_revenue_weighted", "selection_oos_at_freeze": {"freeze": "2024Q2", "n": 4, "wape_link": null, "wape_trend": 23.0, "adopted": "undetermined", "decision": "undetermined", "note": "현재 채택 조합(suppliers_mentions·시차 4·ma4·창 8)을 동결 데이터로 재적합할 수 없음(짝·고객 모델 부족) → 연동 WAPE 없음, undetermined(유의성 조건만으로 채택)"}, "frozen_inputs": "fin(연결/별도)·고객 조선사 모델·지주 자회사 모델은 2025Q2 까지의 분기만; 선표는 체결일 ≤ 2025Q2 말일 계약(원장 최신 금액·코호트 등급, 환산 없음); 잔고는 yards_cache 2025Q2; 시세·환율 forward·prices·forecast_panel 신규수주 미사용. 고객 가중치(suppliers.json 언급 비중)와 합병 체인링크는 현재 지식; 고객 연동 채택은 동결 모델 안에서도 자기 la−4분기 OOS 규칙(selection_oos_at_freeze)", "detail": [{"q": "2025Q3", "rev_pred": 277.78, "rev_act": 285.56, "op_pred": -13.37, "op_act": -50.22}, {"q": "2025Q4", "rev_pred": 411.63, "rev_act": 490.43, "op_pred": -19.81, "op_act": 49.97}, {"q": "2026Q1", "rev_pred": 341.66, "rev_act": 319.14, "op_pred": -16.44, "op_act": 5.34}, {"q": "2026Q2", "rev_pred": 355.91, "rev_act": 367.92, "op_pred": -17.13, "op_act": 31.44}]}</t>
         </is>
       </c>
     </row>
@@ -7537,36 +7537,36 @@
         <v/>
       </c>
       <c r="AC30" s="30" t="n">
-        <v>0.008994815</v>
+        <v>0.008637673</v>
       </c>
       <c r="AD30" s="30" t="n">
-        <v>-0.004005334</v>
+        <v>-0.004379011</v>
       </c>
       <c r="AE30" s="31" t="n"/>
       <c r="AF30" s="30" t="n">
-        <v>0.001147714</v>
+        <v>0.000791705</v>
       </c>
       <c r="AG30" s="30" t="n">
-        <v>0.692791715</v>
+        <v>6.94241951</v>
       </c>
       <c r="AH30" s="30" t="n">
-        <v>0.000923982</v>
+        <v>0.003009043</v>
       </c>
       <c r="AI30" s="30" t="n">
-        <v>-0.000293263</v>
+        <v>-0.008588472999999999</v>
       </c>
       <c r="AJ30" s="31" t="n"/>
       <c r="AK30" s="30" t="n">
-        <v>-0.004374511</v>
+        <v>-0.003047909</v>
       </c>
       <c r="AL30" s="30" t="n">
-        <v>0.688778749</v>
+        <v>6.939725438</v>
       </c>
       <c r="AM30" s="30" t="n">
-        <v>0.008771203999999999</v>
+        <v>0.011795324</v>
       </c>
       <c r="AN30" s="30" t="n">
-        <v>-0.006401408</v>
+        <v>-0.004061584</v>
       </c>
       <c r="AO30" s="31" t="n"/>
     </row>
@@ -7665,36 +7665,36 @@
         <v/>
       </c>
       <c r="AC31" s="30" t="n">
-        <v>0.003494815</v>
+        <v>0.003137673</v>
       </c>
       <c r="AD31" s="30" t="n">
-        <v>0.005994666</v>
+        <v>0.005620989</v>
       </c>
       <c r="AE31" s="31" t="n"/>
       <c r="AF31" s="30" t="n">
-        <v>0.001147714</v>
+        <v>0.000791705</v>
       </c>
       <c r="AG31" s="30" t="n">
-        <v>0.692791715</v>
+        <v>6.94241951</v>
       </c>
       <c r="AH31" s="30" t="n">
-        <v>0.000923982</v>
+        <v>-0.006990957</v>
       </c>
       <c r="AI31" s="30" t="n">
-        <v>-0.010293263</v>
+        <v>0.001411527</v>
       </c>
       <c r="AJ31" s="31" t="n"/>
       <c r="AK31" s="30" t="n">
-        <v>0.005625489</v>
+        <v>-0.003047909</v>
       </c>
       <c r="AL31" s="30" t="n">
-        <v>0.688778749</v>
+        <v>6.939725438</v>
       </c>
       <c r="AM31" s="30" t="n">
-        <v>-0.001228796</v>
+        <v>0.001795324</v>
       </c>
       <c r="AN31" s="30" t="n">
-        <v>0.003598592</v>
+        <v>0.005938416</v>
       </c>
       <c r="AO31" s="31" t="n"/>
     </row>
@@ -7931,26 +7931,26 @@
         <v>3.358e-05</v>
       </c>
       <c r="AG33" s="24" t="n">
-        <v>-0.002602374</v>
+        <v>-0.013095818</v>
       </c>
       <c r="AH33" s="24" t="n">
-        <v>-0.000269333</v>
+        <v>-0.000357258</v>
       </c>
       <c r="AI33" s="24" t="n">
-        <v>-0.007543357</v>
+        <v>-0.007709326</v>
       </c>
       <c r="AJ33" s="25" t="n"/>
       <c r="AK33" s="24" t="n">
-        <v>-0.001526925</v>
+        <v>-0.001629307</v>
       </c>
       <c r="AL33" s="24" t="n">
-        <v>-0.004468837</v>
+        <v>-0.01534048</v>
       </c>
       <c r="AM33" s="24" t="n">
-        <v>-0.001160627</v>
+        <v>-0.001343359</v>
       </c>
       <c r="AN33" s="24" t="n">
-        <v>-0.009107842</v>
+        <v>-0.009468572</v>
       </c>
       <c r="AO33" s="25" t="n"/>
     </row>
@@ -8059,26 +8059,26 @@
         <v>3.8863e-05</v>
       </c>
       <c r="AG34" s="24" t="n">
-        <v>-0.002020778</v>
+        <v>-0.010116842</v>
       </c>
       <c r="AH34" s="24" t="n">
-        <v>-0.000207679</v>
+        <v>-0.000274808</v>
       </c>
       <c r="AI34" s="24" t="n">
-        <v>-0.005816218</v>
+        <v>-0.00592963</v>
       </c>
       <c r="AJ34" s="25" t="n"/>
       <c r="AK34" s="24" t="n">
-        <v>-0.001175272</v>
+        <v>-0.001250938</v>
       </c>
       <c r="AL34" s="24" t="n">
-        <v>-0.003438448</v>
+        <v>-0.011773547</v>
       </c>
       <c r="AM34" s="24" t="n">
-        <v>-0.000892096</v>
+        <v>-0.001027283</v>
       </c>
       <c r="AN34" s="24" t="n">
-        <v>-0.006985569</v>
+        <v>-0.007238441</v>
       </c>
       <c r="AO34" s="25" t="n"/>
     </row>
@@ -8650,7 +8650,7 @@
       </c>
       <c r="AC39" s="32" t="n"/>
       <c r="AD39" s="30" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="AE39" s="31">
         <f>subQ!AE33</f>
@@ -8660,7 +8660,7 @@
       <c r="AG39" s="32" t="n"/>
       <c r="AH39" s="32" t="n"/>
       <c r="AI39" s="30" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="AJ39" s="31">
         <f>subQ!AJ33</f>
@@ -8670,7 +8670,7 @@
       <c r="AL39" s="32" t="n"/>
       <c r="AM39" s="32" t="n"/>
       <c r="AN39" s="30" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="AO39" s="31">
         <f>subQ!AO33</f>
@@ -8860,11 +8860,11 @@
         </is>
       </c>
       <c r="D45" s="30" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>PER 밴드 하단(배) — sector_default(레퍼런스 TP_PE PB 예시 10/15/20배; 과거 PER 중위 36.1배가 캡 5~30 밖 — 턴어라운드 초기 TTM EPS 왜곡)</t>
+          <t>PER 밴드 하단(배) — hist_quarterly(분기 평균가 ÷ TTM EPS, 10분기, 25/50/75 백분위) · 캡 5~30배 적용(원값 1.3/5.4/6.8)</t>
         </is>
       </c>
       <c r="F45" s="9" t="n"/>
@@ -8899,7 +8899,7 @@
         </is>
       </c>
       <c r="D46" s="30" t="n">
-        <v>15</v>
+        <v>5.4</v>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
@@ -8938,7 +8938,7 @@
         </is>
       </c>
       <c r="D47" s="30" t="n">
-        <v>20</v>
+        <v>6.8</v>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
@@ -9133,7 +9133,7 @@
         </is>
       </c>
       <c r="D52" s="36" t="n">
-        <v>0.03042976141288247</v>
+        <v>0.03042783283443792</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -9607,7 +9607,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-08</t>
+          <t>UPDATE: 26-10-09</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -18523,7 +18523,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-08</t>
+          <t>UPDATE: 26-10-09</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -31284,79 +31284,79 @@
           <t>유통주식수</t>
         </is>
       </c>
-      <c r="E30" s="27" t="n">
-        <v>78.88</v>
+      <c r="E30" s="32" t="n">
+        <v>7.8880322</v>
       </c>
       <c r="F30" s="28">
         <f>E30</f>
         <v/>
       </c>
-      <c r="G30" s="27" t="n">
-        <v>78.88</v>
-      </c>
-      <c r="H30" s="27" t="n">
-        <v>78.88</v>
-      </c>
-      <c r="I30" s="27" t="n">
-        <v>78.88</v>
-      </c>
-      <c r="J30" s="27" t="n">
-        <v>78.88</v>
+      <c r="G30" s="32" t="n">
+        <v>7.8880322</v>
+      </c>
+      <c r="H30" s="32" t="n">
+        <v>7.8880322</v>
+      </c>
+      <c r="I30" s="32" t="n">
+        <v>7.8880322</v>
+      </c>
+      <c r="J30" s="32" t="n">
+        <v>7.8880322</v>
       </c>
       <c r="K30" s="28">
         <f>J30</f>
         <v/>
       </c>
-      <c r="L30" s="27" t="n">
-        <v>78.88</v>
-      </c>
-      <c r="M30" s="27" t="n">
-        <v>78.88</v>
-      </c>
-      <c r="N30" s="27" t="n">
-        <v>78.88</v>
-      </c>
-      <c r="O30" s="27" t="n">
-        <v>78.88</v>
+      <c r="L30" s="32" t="n">
+        <v>7.8880322</v>
+      </c>
+      <c r="M30" s="32" t="n">
+        <v>7.8880322</v>
+      </c>
+      <c r="N30" s="32" t="n">
+        <v>7.8880322</v>
+      </c>
+      <c r="O30" s="32" t="n">
+        <v>7.8880322</v>
       </c>
       <c r="P30" s="28">
         <f>O30</f>
         <v/>
       </c>
-      <c r="Q30" s="27" t="n">
-        <v>78.88</v>
-      </c>
-      <c r="R30" s="27" t="n">
-        <v>78.88</v>
-      </c>
-      <c r="S30" s="27" t="n">
-        <v>78.88</v>
-      </c>
-      <c r="T30" s="27" t="n">
-        <v>78.631</v>
+      <c r="Q30" s="32" t="n">
+        <v>7.8880322</v>
+      </c>
+      <c r="R30" s="32" t="n">
+        <v>7.8880322</v>
+      </c>
+      <c r="S30" s="32" t="n">
+        <v>7.8880322</v>
+      </c>
+      <c r="T30" s="32" t="n">
+        <v>7.8630845</v>
       </c>
       <c r="U30" s="28">
         <f>T30</f>
         <v/>
       </c>
-      <c r="V30" s="27" t="n">
-        <v>75.679</v>
-      </c>
-      <c r="W30" s="27" t="n">
-        <v>69.497</v>
-      </c>
-      <c r="X30" s="27" t="n">
-        <v>69.497</v>
-      </c>
-      <c r="Y30" s="27" t="n">
-        <v>69.48099999999999</v>
+      <c r="V30" s="32" t="n">
+        <v>7.5678505</v>
+      </c>
+      <c r="W30" s="32" t="n">
+        <v>6.949711300000001</v>
+      </c>
+      <c r="X30" s="32" t="n">
+        <v>6.949711300000001</v>
+      </c>
+      <c r="Y30" s="32" t="n">
+        <v>6.9481164</v>
       </c>
       <c r="Z30" s="28">
         <f>Y30</f>
         <v/>
       </c>
-      <c r="AA30" s="27" t="n">
-        <v>69.48099999999999</v>
+      <c r="AA30" s="32" t="n">
+        <v>6.9481164</v>
       </c>
       <c r="AB30" s="29" t="n">
         <v>6.945</v>
@@ -31801,8 +31801,8 @@
       <c r="Q33" s="18" t="n"/>
       <c r="R33" s="18" t="n"/>
       <c r="S33" s="18" t="n"/>
-      <c r="T33" s="18" t="n">
-        <v>10</v>
+      <c r="T33" s="20" t="n">
+        <v>100</v>
       </c>
       <c r="U33" s="37">
         <f>SUM(Q33:T33)</f>
@@ -31811,8 +31811,8 @@
       <c r="V33" s="18" t="n"/>
       <c r="W33" s="18" t="n"/>
       <c r="X33" s="18" t="n"/>
-      <c r="Y33" s="18" t="n">
-        <v>10</v>
+      <c r="Y33" s="20" t="n">
+        <v>100</v>
       </c>
       <c r="Z33" s="37">
         <f>SUM(V33:Y33)</f>

--- a/argus/kship/models/085310_model.xlsx
+++ b/argus/kship/models/085310_model.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="변수" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="subQ" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="분기" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TP" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="외화" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="변수" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="subQ" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="분기" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="TP" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="외화" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="변수H">변수!$C$1:$AO$1</definedName>
@@ -4793,35 +4793,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1346.2</v>
+        <v>1345.74</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1458.38</v>
+        <v>1457.79</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -4912,35 +4912,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5031,35 +5031,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>851.8099999999999</v>
+        <v>851.3099999999999</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>919.9299999999999</v>
+        <v>919.5700000000001</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5150,35 +5150,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5269,35 +5269,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1512.43</v>
+        <v>1510.82</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1691.86</v>
+        <v>1690.9</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5388,35 +5388,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5507,35 +5507,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.79</v>
+        <v>200.73</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.89</v>
+        <v>213.82</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5626,35 +5626,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -5761,7 +5761,7 @@
         <v>8930</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>8780</v>
+        <v>8950</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -5943,7 +5943,7 @@
         <v>6950</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>8600</v>
+        <v>8540</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -6034,7 +6034,7 @@
         <v>8774.700000000001</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>8894</v>
+        <v>8928</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -8741,11 +8741,11 @@
         </is>
       </c>
       <c r="D42" s="34" t="n">
-        <v>8780</v>
+        <v>8950</v>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 8,850원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 8,810원)</t>
         </is>
       </c>
       <c r="F42" s="9" t="n"/>
@@ -40291,7 +40291,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/085310_model.xlsx
+++ b/argus/kship/models/085310_model.xlsx
@@ -3922,7 +3922,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-09</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-10</t>
         </is>
       </c>
     </row>
@@ -4793,35 +4793,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1345.74</v>
+        <v>1345.14</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1457.79</v>
+        <v>1457.21</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -4912,35 +4912,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5031,35 +5031,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>851.3099999999999</v>
+        <v>850.79</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>919.5700000000001</v>
+        <v>919.21</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5150,35 +5150,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5269,35 +5269,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1510.82</v>
+        <v>1509.74</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1690.9</v>
+        <v>1689.95</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5388,35 +5388,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5507,35 +5507,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.73</v>
+        <v>200.69</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.82</v>
+        <v>213.75</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5626,35 +5626,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -9607,7 +9607,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-09</t>
+          <t>UPDATE: 26-10-10</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -18523,7 +18523,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-09</t>
+          <t>UPDATE: 26-10-10</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/085310_model.xlsx
+++ b/argus/kship/models/085310_model.xlsx
@@ -3922,7 +3922,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-10</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-11</t>
         </is>
       </c>
     </row>
@@ -9607,7 +9607,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-10</t>
+          <t>UPDATE: 26-10-11</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -18523,7 +18523,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-10</t>
+          <t>UPDATE: 26-10-11</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/085310_model.xlsx
+++ b/argus/kship/models/085310_model.xlsx
@@ -3922,7 +3922,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-11</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-12</t>
         </is>
       </c>
     </row>
@@ -5761,7 +5761,7 @@
         <v>8930</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>8950</v>
+        <v>8760</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -5943,7 +5943,7 @@
         <v>6950</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>8540</v>
+        <v>8410</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -6034,7 +6034,7 @@
         <v>8774.700000000001</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>8928</v>
+        <v>8900</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -8741,7 +8741,7 @@
         </is>
       </c>
       <c r="D42" s="34" t="n">
-        <v>8950</v>
+        <v>8760</v>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
@@ -8781,7 +8781,7 @@
       </c>
       <c r="D43" s="35" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -9607,7 +9607,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-11</t>
+          <t>UPDATE: 26-10-12</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -18523,7 +18523,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-11</t>
+          <t>UPDATE: 26-10-12</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -33183,7 +33183,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -38188,7 +38188,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -40291,7 +40291,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.37</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/085310_model.xlsx
+++ b/argus/kship/models/085310_model.xlsx
@@ -3922,7 +3922,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-12</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-13</t>
         </is>
       </c>
     </row>
@@ -4793,35 +4793,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1345.14</v>
+        <v>1343.63</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1457.21</v>
+        <v>1456.58</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -4912,35 +4912,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5031,35 +5031,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>850.79</v>
+        <v>849.51</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>919.21</v>
+        <v>918.8099999999999</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5150,35 +5150,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5269,35 +5269,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1509.74</v>
+        <v>1507.34</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1689.95</v>
+        <v>1688.95</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5388,35 +5388,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5507,35 +5507,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.69</v>
+        <v>200.5</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.75</v>
+        <v>213.68</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5626,35 +5626,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -5761,7 +5761,7 @@
         <v>8930</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>8760</v>
+        <v>8950</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -5943,7 +5943,7 @@
         <v>6950</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>8410</v>
+        <v>8220</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -6034,7 +6034,7 @@
         <v>8774.700000000001</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>8900</v>
+        <v>8874.299999999999</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -8741,11 +8741,11 @@
         </is>
       </c>
       <c r="D42" s="34" t="n">
-        <v>8760</v>
+        <v>8950</v>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 8,810원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 8,780원)</t>
         </is>
       </c>
       <c r="F42" s="9" t="n"/>
@@ -8781,7 +8781,7 @@
       </c>
       <c r="D43" s="35" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -9607,7 +9607,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-12</t>
+          <t>UPDATE: 26-10-13</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -18523,7 +18523,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-12</t>
+          <t>UPDATE: 26-10-13</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -33183,7 +33183,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -38188,7 +38188,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -40291,7 +40291,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/085310_model.xlsx
+++ b/argus/kship/models/085310_model.xlsx
@@ -3922,7 +3922,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-13</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-14</t>
         </is>
       </c>
     </row>
@@ -4793,35 +4793,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1343.63</v>
+        <v>1343.39</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1456.58</v>
+        <v>1456.01</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -4912,35 +4912,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5031,35 +5031,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>849.51</v>
+        <v>849.39</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>918.8099999999999</v>
+        <v>918.46</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5150,35 +5150,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5269,35 +5269,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1507.34</v>
+        <v>1506.62</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1688.95</v>
+        <v>1688.01</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5388,35 +5388,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5507,35 +5507,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.5</v>
+        <v>200.49</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.68</v>
+        <v>213.61</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5626,35 +5626,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -5761,7 +5761,7 @@
         <v>8930</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>8950</v>
+        <v>8750</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6034,7 +6034,7 @@
         <v>8774.700000000001</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>8874.299999999999</v>
+        <v>8856.200000000001</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -8741,11 +8741,11 @@
         </is>
       </c>
       <c r="D42" s="34" t="n">
-        <v>8950</v>
+        <v>8750</v>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 8,780원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 8,740원)</t>
         </is>
       </c>
       <c r="F42" s="9" t="n"/>
@@ -8781,7 +8781,7 @@
       </c>
       <c r="D43" s="35" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -9607,7 +9607,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-13</t>
+          <t>UPDATE: 26-10-14</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -18523,7 +18523,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-13</t>
+          <t>UPDATE: 26-10-14</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -33183,7 +33183,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -38188,7 +38188,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -40291,7 +40291,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.37</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/085310_model.xlsx
+++ b/argus/kship/models/085310_model.xlsx
@@ -3922,7 +3922,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-14</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-19</t>
         </is>
       </c>
     </row>
@@ -4793,35 +4793,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1343.39</v>
+        <v>1342.11</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1456.01</v>
+        <v>1454.27</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -4912,35 +4912,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5031,35 +5031,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>849.39</v>
+        <v>848.59</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>918.46</v>
+        <v>917.39</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5150,35 +5150,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5269,35 +5269,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1506.62</v>
+        <v>1505.3</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1688.01</v>
+        <v>1685.25</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5388,35 +5388,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5507,35 +5507,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.49</v>
+        <v>200.38</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.61</v>
+        <v>213.41</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5626,35 +5626,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -5761,7 +5761,7 @@
         <v>8930</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>8750</v>
+        <v>9430</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -5943,7 +5943,7 @@
         <v>6950</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>8220</v>
+        <v>8170</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -6034,7 +6034,7 @@
         <v>8774.700000000001</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>8856.200000000001</v>
+        <v>8882.700000000001</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -8741,11 +8741,11 @@
         </is>
       </c>
       <c r="D42" s="34" t="n">
-        <v>8750</v>
+        <v>9430</v>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 8,740원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 8,680원)</t>
         </is>
       </c>
       <c r="F42" s="9" t="n"/>
@@ -8781,7 +8781,7 @@
       </c>
       <c r="D43" s="35" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -9607,7 +9607,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-14</t>
+          <t>UPDATE: 26-10-19</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -18523,7 +18523,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-14</t>
+          <t>UPDATE: 26-10-19</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -33183,7 +33183,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -38188,7 +38188,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -40291,7 +40291,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.36</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/085310_model.xlsx
+++ b/argus/kship/models/085310_model.xlsx
@@ -3922,7 +3922,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-19</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-26</t>
         </is>
       </c>
     </row>
@@ -4793,35 +4793,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1342.11</v>
+        <v>1337.49</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1454.27</v>
+        <v>1451.19</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -4912,35 +4912,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5031,35 +5031,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>848.59</v>
+        <v>846.51</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>917.39</v>
+        <v>915.5700000000001</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5150,35 +5150,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5269,35 +5269,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1505.3</v>
+        <v>1500.06</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1685.25</v>
+        <v>1680.5</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5388,35 +5388,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5507,35 +5507,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.38</v>
+        <v>199.88</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.41</v>
+        <v>213.06</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5626,35 +5626,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -5761,7 +5761,7 @@
         <v>8930</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>9430</v>
+        <v>8600</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6034,7 +6034,7 @@
         <v>8774.700000000001</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>8882.700000000001</v>
+        <v>8905</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -8741,11 +8741,11 @@
         </is>
       </c>
       <c r="D42" s="34" t="n">
-        <v>9430</v>
+        <v>8600</v>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 8,680원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 9,000원)</t>
         </is>
       </c>
       <c r="F42" s="9" t="n"/>
@@ -8781,7 +8781,7 @@
       </c>
       <c r="D43" s="35" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261026</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -9607,7 +9607,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-19</t>
+          <t>UPDATE: 26-10-26</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -18523,7 +18523,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-19</t>
+          <t>UPDATE: 26-10-26</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -33183,7 +33183,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261026</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -38188,7 +38188,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261026</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -40291,7 +40291,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.39</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="33">
